--- a/project/outputs_xlsx_solution/test_1.4-wide-NC-1.xlsx
+++ b/project/outputs_xlsx_solution/test_1.4-wide-NC-1.xlsx
@@ -957,7 +957,7 @@
         <v>16</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="N14" t="s">
         <v>14</v>
